--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_265_R27.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_265_R27.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.367699999999999</v>
+        <v>9.847</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5167</v>
+        <v>5.0632</v>
       </c>
       <c r="F2" t="n">
-        <v>4.851</v>
+        <v>4.7838</v>
       </c>
       <c r="G2" t="n">
         <v>6.7458</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0018</v>
+        <v>0.4775</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0376</v>
+        <v>-0.4911</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0359</v>
+        <v>0.9687</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. PAYNE</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7408</v>
+        <v>5.1898</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9001</v>
+        <v>1.296</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8407</v>
+        <v>3.8938</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2154</v>
+        <v>2.4949</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0455</v>
+        <v>0.9725</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8300999999999999</v>
+        <v>1.5224</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0684</v>
+        <v>1.8304</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5242</v>
+        <v>0.7765</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.4559</v>
+        <v>1.0539</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1471</v>
+        <v>0.6645</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5213</v>
+        <v>0.196</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6258</v>
+        <v>0.4685</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6959</v>
+        <v>2.7834</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0154</v>
+        <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7573</v>
+        <v>-0.0885</v>
       </c>
       <c r="T3" t="n">
-        <v>0.543</v>
+        <v>-0.5344</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2144</v>
+        <v>0.4459</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>C. PAYNE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.694</v>
+        <v>4.3334</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8675</v>
+        <v>0.2238</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8266</v>
+        <v>4.1096</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4949</v>
+        <v>2.2154</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9725</v>
+        <v>3.0455</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5224</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8304</v>
+        <v>1.0684</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7765</v>
+        <v>2.5242</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0539</v>
+        <v>-1.4559</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6645</v>
+        <v>1.1471</v>
       </c>
       <c r="N4" t="n">
-        <v>0.196</v>
+        <v>0.5213</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4685</v>
+        <v>0.6258</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7834</v>
+        <v>0.6959</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7834</v>
+        <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5843</v>
+        <v>0.3499</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.963</v>
+        <v>-0.1333</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3787</v>
+        <v>0.4832</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3222</v>
+        <v>4.2961</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8213</v>
+        <v>-0.7467</v>
       </c>
       <c r="F5" t="n">
-        <v>5.1436</v>
+        <v>5.0427</v>
       </c>
       <c r="G5" t="n">
         <v>1.7094</v>
@@ -844,13 +844,13 @@
         <v>3.0154</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8448</v>
+        <v>0.8186</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1687</v>
+        <v>-0.094</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0135</v>
+        <v>0.9127</v>
       </c>
       <c r="V5" t="n">
         <v>1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. JEKIRI</t>
+          <t>N. CALATHES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0258</v>
+        <v>3.3159</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5054</v>
+        <v>1.1893</v>
       </c>
       <c r="F6" t="n">
-        <v>4.5312</v>
+        <v>2.1266</v>
       </c>
       <c r="G6" t="n">
-        <v>0.269</v>
+        <v>1.4617</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0996</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3686</v>
+        <v>0.6659</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5345</v>
+        <v>1.4015</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6449</v>
+        <v>1.3647</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1104</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8035</v>
+        <v>0.0602</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4547</v>
+        <v>-0.5688</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2582</v>
+        <v>0.6291</v>
       </c>
       <c r="P6" t="n">
         <v>2.0876</v>
@@ -922,28 +922,28 @@
         <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>0.275</v>
+        <v>0.3027</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9709</v>
+        <v>-0.2122</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2459</v>
+        <v>0.5149</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>T. JEKIRI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9877</v>
+        <v>3.075</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0487</v>
+        <v>-1.1201</v>
       </c>
       <c r="F7" t="n">
-        <v>1.939</v>
+        <v>4.1951</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4039</v>
+        <v>0.269</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.143</v>
+        <v>-1.0996</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2609</v>
+        <v>1.3686</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2824</v>
+        <v>-0.5345</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3929</v>
+        <v>-0.6449</v>
       </c>
       <c r="L7" t="n">
         <v>0.1104</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1215</v>
+        <v>0.8035</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2499</v>
+        <v>-0.4547</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3713</v>
+        <v>1.2582</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7859</v>
+        <v>0.3242</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2047</v>
+        <v>-0.5856</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5812</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>1.214</v>
+        <v>0.3943</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. CALATHES</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8709</v>
+        <v>2.7256</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8787</v>
+        <v>0.8875</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9921</v>
+        <v>1.8382</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4617</v>
+        <v>-0.4039</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7959000000000001</v>
+        <v>-0.143</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6659</v>
+        <v>-0.2609</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4015</v>
+        <v>-0.2824</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3647</v>
+        <v>-0.3929</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>0.1104</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0602</v>
+        <v>-0.1215</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5688</v>
+        <v>0.2499</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6291</v>
+        <v>-0.3713</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1423</v>
+        <v>0.5239</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5228</v>
+        <v>0.0435</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3804</v>
+        <v>0.4804</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5361</v>
+        <v>1.214</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.572</v>
+        <v>-1.4129</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.4224</v>
+        <v>-4.2298</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8504</v>
+        <v>2.8168</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9952</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1191</v>
+        <v>0.2781</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4481</v>
+        <v>-0.2555</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5671</v>
+        <v>0.5335</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8083</v>
+        <v>-2.3729</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0203</v>
+        <v>-1.753</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7879</v>
+        <v>-0.6199</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1063</v>
@@ -1234,13 +1234,13 @@
         <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4854</v>
+        <v>-0.0501</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5149</v>
+        <v>-0.2475</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0294</v>
+        <v>0.1975</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6083</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9668</v>
+        <v>-2.8585</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1701</v>
+        <v>-2.0955</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7967</v>
+        <v>-0.7631</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9971</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2016</v>
+        <v>-0.0934</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>-0.1494</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4871</v>
+        <v>-3.8431</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7252</v>
+        <v>-4.0477</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2382</v>
+        <v>0.2046</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9394</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5399</v>
+        <v>0.1838</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2715</v>
+        <v>-0.051</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2684</v>
+        <v>0.2348</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5361</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>21.1749</v>
+        <v>22.2954</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.452999999999999</v>
+        <v>-5.332999999999999</v>
       </c>
       <c r="F13" t="n">
         <v>27.6282</v>
@@ -1435,13 +1435,13 @@
         <v>9.4543</v>
       </c>
       <c r="H13" t="n">
-        <v>7.346700000000001</v>
+        <v>7.346699999999999</v>
       </c>
       <c r="I13" t="n">
         <v>2.1079</v>
       </c>
       <c r="J13" t="n">
-        <v>6.044500000000002</v>
+        <v>6.0445</v>
       </c>
       <c r="K13" t="n">
         <v>8.370799999999999</v>
@@ -1468,13 +1468,13 @@
         <v>23.1953</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9066</v>
+        <v>3.0267</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.8308</v>
+        <v>-2.7105</v>
       </c>
       <c r="U13" t="n">
-        <v>5.7373</v>
+        <v>5.7374</v>
       </c>
       <c r="V13" t="n">
         <v>0.5361</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4331</v>
+        <v>3.9065</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4485</v>
+        <v>0.741</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9846</v>
+        <v>3.1656</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8258</v>
+        <v>2.1852</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.9434</v>
+        <v>1.9576</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1176</v>
+        <v>0.2276</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.08160000000000001</v>
+        <v>2.6755</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3123</v>
+        <v>3.3883</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2308</v>
+        <v>-0.7127</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7442</v>
+        <v>-0.4903</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.631</v>
+        <v>-1.4306</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8868</v>
+        <v>0.9403</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.6959</v>
+        <v>-3.7112</v>
       </c>
       <c r="R14" t="n">
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>1.563</v>
+        <v>0.4325</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1537</v>
+        <v>-0.9039</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4093</v>
+        <v>1.3364</v>
       </c>
       <c r="V14" t="n">
-        <v>1.0722</v>
+        <v>2.6805</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0722</v>
+        <v>2.6805</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2939</v>
+        <v>2.5974</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1512</v>
+        <v>-0.1412</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1427</v>
+        <v>2.7386</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1852</v>
+        <v>-0.8258</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9576</v>
+        <v>-1.9434</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2276</v>
+        <v>1.1176</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6755</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3883</v>
+        <v>-0.3123</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7127</v>
+        <v>0.2308</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4903</v>
+        <v>-0.7442</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4306</v>
+        <v>-1.631</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9403</v>
+        <v>0.8868</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.7112</v>
+        <v>-0.6959</v>
       </c>
       <c r="R15" t="n">
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1801</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4936</v>
+        <v>-0.436</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3135</v>
+        <v>1.1633</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6805</v>
+        <v>1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6805</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0374</v>
       </c>
       <c r="E16" t="n">
         <v>-0.9357</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8647</v>
+        <v>0.8984</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4826</v>
@@ -1702,13 +1702,13 @@
         <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0523</v>
+        <v>-0.0187</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.1307</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>V. TOLIOPOULOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1155</v>
+        <v>-0.1293</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-1.5737</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7378</v>
+        <v>1.4444</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4412</v>
+        <v>0.7302</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8428</v>
+        <v>0.3253</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4016</v>
+        <v>0.4049</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4135</v>
+        <v>-0.0956</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3767</v>
+        <v>-0.4502</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0368</v>
+        <v>0.3546</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8547</v>
+        <v>0.8258</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2195</v>
+        <v>0.7756</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3648</v>
+        <v>0.0502</v>
       </c>
       <c r="P17" t="n">
         <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.6237</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.952</v>
+        <v>-0.0914</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7512</v>
+        <v>-0.3183</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2008</v>
+        <v>0.2269</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3943</v>
+        <v>-0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4082</v>
+        <v>-0.3292</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3874</v>
+        <v>-1.3251</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9791</v>
+        <v>0.9959</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4532</v>
+        <v>-0.4412</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5606</v>
+        <v>-0.8428</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0138</v>
+        <v>0.4016</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4604</v>
+        <v>0.4135</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2892</v>
+        <v>0.3767</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0071</v>
+        <v>-0.8547</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2714</v>
+        <v>-1.2195</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2643</v>
+        <v>0.3648</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-1.6237</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2227</v>
+        <v>0.7382</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8215</v>
+        <v>0.2794</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0442</v>
+        <v>0.4589</v>
       </c>
       <c r="V18" t="n">
-        <v>1.214</v>
+        <v>-0.3943</v>
       </c>
       <c r="W18" t="n">
-        <v>1.214</v>
+        <v>-0.3943</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>V. TOLIOPOULOS</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8756</v>
+        <v>-0.7715</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9275</v>
+        <v>-2.2694</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0519</v>
+        <v>1.4979</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7302</v>
+        <v>-0.4532</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3253</v>
+        <v>0.5606</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4049</v>
+        <v>-1.0138</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0956</v>
+        <v>-0.4604</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4502</v>
+        <v>0.2892</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3546</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8258</v>
+        <v>0.0071</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7756</v>
+        <v>0.2714</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0502</v>
+        <v>-0.2643</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8377</v>
+        <v>-0.1406</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6721</v>
+        <v>-0.7035</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1656</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5361</v>
+        <v>1.214</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1462</v>
+        <v>-3.079</v>
       </c>
       <c r="E20" t="n">
         <v>-1.457</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6892</v>
+        <v>-1.622</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6525</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2618</v>
+        <v>-0.1946</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.794</v>
+        <v>-3.9392</v>
       </c>
       <c r="E21" t="n">
         <v>-2.7189</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0751</v>
+        <v>-1.2203</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4861</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3079</v>
+        <v>-0.4531</v>
       </c>
       <c r="T21" t="n">
         <v>-0.9709</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6629</v>
+        <v>0.5177</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6418</v>
+        <v>-4.1262</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3253</v>
+        <v>-4.5612</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3165</v>
+        <v>0.4349</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3281</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7622</v>
+        <v>-0.2467</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1845</v>
+        <v>-0.4204</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5777</v>
+        <v>0.1737</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0092</v>
+        <v>-4.6224</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6217</v>
+        <v>-3.5038</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3875</v>
+        <v>-1.1187</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2794</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1062</v>
+        <v>-0.7194</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9709</v>
+        <v>-0.8529</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1353</v>
+        <v>0.1336</v>
       </c>
       <c r="V24" t="n">
         <v>0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.8299</v>
+        <v>-5.0614</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.9464</v>
+        <v>-5.8285</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1165</v>
+        <v>0.7671</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9514</v>
@@ -2404,13 +2404,13 @@
         <v>2.0876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5228</v>
+        <v>0.2458</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4832</v>
+        <v>-0.3653</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0395</v>
+        <v>0.6111</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8919</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-21.175</v>
+        <v>-19.6023</v>
       </c>
       <c r="E26" t="n">
         <v>-26.6978</v>
       </c>
       <c r="F26" t="n">
-        <v>5.522699999999999</v>
+        <v>7.0955</v>
       </c>
       <c r="G26" t="n">
         <v>-9.454499999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-7.3467</v>
+        <v>-7.346699999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-2.1077</v>
@@ -2482,16 +2482,16 @@
         <v>13.9172</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.9066</v>
+        <v>-0.3340000000000002</v>
       </c>
       <c r="T26" t="n">
         <v>-5.737400000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>3.8308</v>
+        <v>5.403700000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.5361</v>
+        <v>-0.5361000000000002</v>
       </c>
       <c r="W26" t="n">
         <v>5.644600000000001</v>
